--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:13</t>
+    <t xml:space="preserve">2026-09-09 22:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_valparaiso.xlsx
@@ -62,12 +62,12 @@
     <t xml:space="preserve">Promedio Regional</t>
   </si>
   <si>
+    <t xml:space="preserve">Marga Marga</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quillota</t>
   </si>
   <si>
-    <t xml:space="preserve">Marga Marga</t>
-  </si>
-  <si>
     <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:11</t>
+    <t xml:space="preserve">2026-09-17 13:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -809,16 +809,16 @@
         <v>8</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>684362</v>
+        <v>726130</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>599435</v>
+        <v>632310</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>84927</v>
+        <v>93820</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>14.17</v>
+        <v>14.84</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>5</v>
@@ -832,16 +832,16 @@
         <v>9</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>909550</v>
+        <v>871527.5</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>804006</v>
+        <v>772170</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>105544</v>
+        <v>99357.5</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>13.13</v>
+        <v>12.87</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5</v>
@@ -858,13 +858,13 @@
         <v>800000</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>704000</v>
+        <v>706110</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>96000</v>
+        <v>93890</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>13.64</v>
+        <v>13.3</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>5</v>
@@ -878,16 +878,16 @@
         <v>8</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>726130</v>
+        <v>684362</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>632310</v>
+        <v>599435</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>93820</v>
+        <v>84927</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>14.84</v>
+        <v>14.17</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>4</v>
@@ -901,16 +901,16 @@
         <v>9</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>871527.5</v>
+        <v>909550</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>772170</v>
+        <v>804006</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>99357.5</v>
+        <v>105544</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>12.87</v>
+        <v>13.13</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>4</v>
@@ -927,13 +927,13 @@
         <v>800000</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>706110</v>
+        <v>704000</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>93890</v>
+        <v>96000</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>13.3</v>
+        <v>13.64</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>4</v>
@@ -1243,18 +1243,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>896030</v>
+        <v>802380</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>800000</v>
+        <v>896030</v>
       </c>
     </row>
     <row r="4">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>800000</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>802380</v>
+        <v>800000</v>
       </c>
     </row>
   </sheetData>
@@ -1327,101 +1327,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>877160</v>
+        <v>708330</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>995600</v>
+        <v>802380</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1052917</v>
+        <v>862500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>777105</v>
+        <v>877160</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>896030</v>
+        <v>995600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>951280</v>
+        <v>1052917</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>706110</v>
+        <v>777105</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>800000</v>
+        <v>896030</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>862813</v>
+        <v>951280</v>
       </c>
     </row>
     <row r="11">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>35</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>32</v>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>36</v>
@@ -1558,35 +1558,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>708330</v>
+        <v>706110</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>802380</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>862500</v>
+        <v>862813</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:40</t>
+    <t xml:space="preserve">2026-09-25 21:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:37</t>
+    <t xml:space="preserve">2026-10-05 07:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -751,7 +751,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>712068</v>
+        <v>712069</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>867662</v>
@@ -796,7 +796,7 @@
         <v>733090</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>863246</v>
+        <v>863247</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>-15.1</v>
